--- a/media/Levels/Level_8.xlsx
+++ b/media/Levels/Level_8.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC01F261-1A84-453E-B91F-F0FE955ED1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34D34B72-7BF8-4F82-A441-D0B8328CA234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Level_2" sheetId="1" r:id="rId1"/>
+    <sheet name="Level_8" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -5188,20 +5188,20 @@
       <c r="U10" s="3">
         <v>0</v>
       </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>0</v>
+      <c r="V10">
+        <v>13</v>
+      </c>
+      <c r="W10">
+        <v>13</v>
+      </c>
+      <c r="X10">
+        <v>13</v>
+      </c>
+      <c r="Y10">
+        <v>13</v>
+      </c>
+      <c r="Z10">
+        <v>13</v>
       </c>
       <c r="AA10">
         <v>13</v>
@@ -6099,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
         <v>0</v>
@@ -6551,7 +6551,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y13" s="3">
         <v>0</v>
@@ -7448,14 +7448,14 @@
       <c r="U15">
         <v>13</v>
       </c>
-      <c r="V15">
-        <v>13</v>
-      </c>
-      <c r="W15">
-        <v>13</v>
-      </c>
-      <c r="X15">
-        <v>13</v>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -7463,14 +7463,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AA15">
+        <v>13</v>
+      </c>
+      <c r="AB15">
+        <v>13</v>
+      </c>
+      <c r="AC15">
+        <v>13</v>
       </c>
       <c r="AD15">
         <v>13</v>
@@ -8368,7 +8368,7 @@
         <v>0</v>
       </c>
       <c r="AA17" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="3">
         <v>0</v>
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="AA18" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AB18" s="3">
         <v>0</v>
@@ -10628,7 +10628,7 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="AA23" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AB23" s="3">
         <v>0</v>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="AA27" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="3">
         <v>0</v>
@@ -13340,7 +13340,7 @@
         <v>0</v>
       </c>
       <c r="AA28" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AB28" s="3">
         <v>0</v>
@@ -14225,8 +14225,8 @@
       <c r="T30">
         <v>13</v>
       </c>
-      <c r="U30">
-        <v>13</v>
+      <c r="U30" s="3">
+        <v>0</v>
       </c>
       <c r="V30" s="3">
         <v>0</v>
@@ -14243,14 +14243,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-      <c r="AA30">
-        <v>13</v>
-      </c>
-      <c r="AB30">
-        <v>13</v>
-      </c>
-      <c r="AC30">
-        <v>13</v>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
       </c>
       <c r="AD30">
         <v>13</v>
@@ -14677,8 +14677,8 @@
       <c r="T31">
         <v>13</v>
       </c>
-      <c r="U31">
-        <v>13</v>
+      <c r="U31" s="3">
+        <v>0</v>
       </c>
       <c r="V31" s="3">
         <v>0</v>
@@ -14692,8 +14692,8 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-      <c r="Z31" s="3">
-        <v>0</v>
+      <c r="Z31">
+        <v>13</v>
       </c>
       <c r="AA31">
         <v>13</v>
@@ -15129,23 +15129,23 @@
       <c r="T32">
         <v>13</v>
       </c>
-      <c r="U32">
-        <v>13</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X32" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
+      <c r="Z32">
+        <v>13</v>
       </c>
       <c r="AA32">
         <v>13</v>
@@ -15581,8 +15581,8 @@
       <c r="T33" s="2">
         <v>8</v>
       </c>
-      <c r="U33">
-        <v>13</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3">
         <v>0</v>
@@ -15596,8 +15596,8 @@
       <c r="Y33" s="3">
         <v>0</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
+      <c r="Z33">
+        <v>13</v>
       </c>
       <c r="AA33">
         <v>13</v>
@@ -16033,7 +16033,7 @@
       <c r="T34">
         <v>13</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="3">
         <v>0</v>
       </c>
       <c r="V34" s="3">
@@ -16048,8 +16048,8 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-      <c r="Z34" s="3">
-        <v>0</v>
+      <c r="Z34">
+        <v>13</v>
       </c>
       <c r="AA34">
         <v>13</v>
@@ -55420,65 +55420,65 @@
       <c r="AP121">
         <v>13</v>
       </c>
-      <c r="AQ121">
-        <v>13</v>
-      </c>
-      <c r="AR121">
-        <v>13</v>
-      </c>
-      <c r="AS121">
-        <v>13</v>
-      </c>
-      <c r="AT121">
-        <v>13</v>
-      </c>
-      <c r="AU121">
-        <v>13</v>
-      </c>
-      <c r="AV121">
-        <v>13</v>
-      </c>
-      <c r="AW121">
-        <v>13</v>
-      </c>
-      <c r="AX121">
-        <v>13</v>
-      </c>
-      <c r="AY121">
-        <v>13</v>
-      </c>
-      <c r="AZ121">
-        <v>13</v>
-      </c>
-      <c r="BA121">
-        <v>13</v>
-      </c>
-      <c r="BB121">
-        <v>13</v>
+      <c r="AQ121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY121" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB121" s="4">
+        <v>0</v>
       </c>
       <c r="BC121" s="2">
         <v>8</v>
       </c>
-      <c r="BD121">
-        <v>13</v>
-      </c>
-      <c r="BE121">
-        <v>13</v>
-      </c>
-      <c r="BF121">
-        <v>13</v>
-      </c>
-      <c r="BG121">
-        <v>13</v>
-      </c>
-      <c r="BH121">
-        <v>13</v>
-      </c>
-      <c r="BI121">
-        <v>13</v>
-      </c>
-      <c r="BJ121">
-        <v>13</v>
+      <c r="BD121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI121" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ121" s="4">
+        <v>0</v>
       </c>
       <c r="BK121">
         <v>13</v>
@@ -55558,65 +55558,65 @@
       <c r="CJ121">
         <v>13</v>
       </c>
-      <c r="CK121">
-        <v>13</v>
-      </c>
-      <c r="CL121">
-        <v>13</v>
-      </c>
-      <c r="CM121">
-        <v>13</v>
-      </c>
-      <c r="CN121">
-        <v>13</v>
-      </c>
-      <c r="CO121">
-        <v>13</v>
-      </c>
-      <c r="CP121">
-        <v>13</v>
+      <c r="CK121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CL121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CM121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CN121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CO121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CP121" s="4">
+        <v>0</v>
       </c>
       <c r="CQ121" s="2">
         <v>6</v>
       </c>
-      <c r="CR121">
-        <v>13</v>
-      </c>
-      <c r="CS121">
-        <v>13</v>
-      </c>
-      <c r="CT121">
-        <v>13</v>
-      </c>
-      <c r="CU121">
-        <v>13</v>
-      </c>
-      <c r="CV121">
-        <v>13</v>
-      </c>
-      <c r="CW121">
-        <v>13</v>
-      </c>
-      <c r="CX121">
-        <v>13</v>
-      </c>
-      <c r="CY121">
-        <v>13</v>
-      </c>
-      <c r="CZ121">
-        <v>13</v>
-      </c>
-      <c r="DA121">
-        <v>13</v>
-      </c>
-      <c r="DB121">
-        <v>13</v>
-      </c>
-      <c r="DC121">
-        <v>13</v>
-      </c>
-      <c r="DD121">
-        <v>13</v>
+      <c r="CR121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CS121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CT121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CU121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CV121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CW121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CX121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CY121" s="4">
+        <v>0</v>
+      </c>
+      <c r="CZ121" s="4">
+        <v>0</v>
+      </c>
+      <c r="DA121" s="4">
+        <v>0</v>
+      </c>
+      <c r="DB121" s="4">
+        <v>0</v>
+      </c>
+      <c r="DC121" s="4">
+        <v>0</v>
+      </c>
+      <c r="DD121" s="4">
+        <v>0</v>
       </c>
       <c r="DE121">
         <v>13</v>
@@ -55872,65 +55872,65 @@
       <c r="AP122">
         <v>13</v>
       </c>
-      <c r="AQ122">
-        <v>13</v>
-      </c>
-      <c r="AR122">
-        <v>13</v>
-      </c>
-      <c r="AS122">
-        <v>13</v>
-      </c>
-      <c r="AT122">
-        <v>13</v>
-      </c>
-      <c r="AU122">
-        <v>13</v>
-      </c>
-      <c r="AV122">
-        <v>13</v>
-      </c>
-      <c r="AW122">
-        <v>13</v>
-      </c>
-      <c r="AX122">
-        <v>13</v>
-      </c>
-      <c r="AY122">
-        <v>13</v>
-      </c>
-      <c r="AZ122">
-        <v>13</v>
-      </c>
-      <c r="BA122">
-        <v>13</v>
-      </c>
-      <c r="BB122">
-        <v>13</v>
-      </c>
-      <c r="BC122">
-        <v>13</v>
-      </c>
-      <c r="BD122" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE122">
-        <v>13</v>
-      </c>
-      <c r="BF122">
-        <v>13</v>
-      </c>
-      <c r="BG122">
-        <v>13</v>
-      </c>
-      <c r="BH122">
-        <v>13</v>
-      </c>
-      <c r="BI122">
-        <v>13</v>
-      </c>
-      <c r="BJ122">
-        <v>13</v>
+      <c r="AQ122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY122" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BA122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BB122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BC122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ122" s="4">
+        <v>0</v>
       </c>
       <c r="BK122">
         <v>13</v>
@@ -59968,7 +59968,7 @@
         <v>0</v>
       </c>
       <c r="AZ131" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BA131" s="4">
         <v>0</v>
@@ -60106,7 +60106,7 @@
         <v>0</v>
       </c>
       <c r="CT131" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="CU131" s="4">
         <v>0</v>
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="CT132" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CU132" s="4">
         <v>0</v>
@@ -60872,7 +60872,7 @@
         <v>0</v>
       </c>
       <c r="AZ133" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BA133" s="4">
         <v>0</v>
@@ -64460,65 +64460,65 @@
       <c r="AP141">
         <v>13</v>
       </c>
-      <c r="AQ141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AY141" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BA141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BC141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BD141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI141" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ141" s="4">
-        <v>0</v>
+      <c r="AQ141">
+        <v>13</v>
+      </c>
+      <c r="AR141">
+        <v>13</v>
+      </c>
+      <c r="AS141">
+        <v>13</v>
+      </c>
+      <c r="AT141">
+        <v>13</v>
+      </c>
+      <c r="AU141">
+        <v>13</v>
+      </c>
+      <c r="AV141">
+        <v>13</v>
+      </c>
+      <c r="AW141">
+        <v>13</v>
+      </c>
+      <c r="AX141">
+        <v>13</v>
+      </c>
+      <c r="AY141">
+        <v>13</v>
+      </c>
+      <c r="AZ141">
+        <v>13</v>
+      </c>
+      <c r="BA141">
+        <v>13</v>
+      </c>
+      <c r="BB141">
+        <v>13</v>
+      </c>
+      <c r="BC141">
+        <v>13</v>
+      </c>
+      <c r="BD141">
+        <v>13</v>
+      </c>
+      <c r="BE141">
+        <v>13</v>
+      </c>
+      <c r="BF141">
+        <v>13</v>
+      </c>
+      <c r="BG141">
+        <v>13</v>
+      </c>
+      <c r="BH141">
+        <v>13</v>
+      </c>
+      <c r="BI141">
+        <v>13</v>
+      </c>
+      <c r="BJ141">
+        <v>13</v>
       </c>
       <c r="BK141">
         <v>13</v>
@@ -64598,65 +64598,65 @@
       <c r="CJ141">
         <v>13</v>
       </c>
-      <c r="CK141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CL141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CM141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CN141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CO141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CP141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CQ141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CR141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CS141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CT141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CU141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CV141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CW141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CX141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CY141" s="4">
-        <v>0</v>
-      </c>
-      <c r="CZ141" s="4">
-        <v>0</v>
-      </c>
-      <c r="DA141" s="4">
-        <v>0</v>
-      </c>
-      <c r="DB141" s="4">
-        <v>0</v>
-      </c>
-      <c r="DC141" s="4">
-        <v>0</v>
-      </c>
-      <c r="DD141" s="4">
-        <v>0</v>
+      <c r="CK141">
+        <v>13</v>
+      </c>
+      <c r="CL141">
+        <v>13</v>
+      </c>
+      <c r="CM141">
+        <v>13</v>
+      </c>
+      <c r="CN141">
+        <v>13</v>
+      </c>
+      <c r="CO141">
+        <v>13</v>
+      </c>
+      <c r="CP141">
+        <v>13</v>
+      </c>
+      <c r="CQ141">
+        <v>13</v>
+      </c>
+      <c r="CR141">
+        <v>13</v>
+      </c>
+      <c r="CS141">
+        <v>13</v>
+      </c>
+      <c r="CT141">
+        <v>13</v>
+      </c>
+      <c r="CU141">
+        <v>13</v>
+      </c>
+      <c r="CV141">
+        <v>13</v>
+      </c>
+      <c r="CW141">
+        <v>13</v>
+      </c>
+      <c r="CX141">
+        <v>13</v>
+      </c>
+      <c r="CY141">
+        <v>13</v>
+      </c>
+      <c r="CZ141">
+        <v>13</v>
+      </c>
+      <c r="DA141">
+        <v>13</v>
+      </c>
+      <c r="DB141">
+        <v>13</v>
+      </c>
+      <c r="DC141">
+        <v>13</v>
+      </c>
+      <c r="DD141">
+        <v>13</v>
       </c>
       <c r="DE141">
         <v>13</v>
@@ -64912,65 +64912,65 @@
       <c r="AP142">
         <v>13</v>
       </c>
-      <c r="AQ142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AU142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AV142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AW142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AX142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AY142" s="4">
-        <v>0</v>
-      </c>
-      <c r="AZ142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BA142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BC142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BD142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI142" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ142" s="4">
-        <v>0</v>
+      <c r="AQ142">
+        <v>13</v>
+      </c>
+      <c r="AR142">
+        <v>13</v>
+      </c>
+      <c r="AS142">
+        <v>13</v>
+      </c>
+      <c r="AT142">
+        <v>13</v>
+      </c>
+      <c r="AU142">
+        <v>13</v>
+      </c>
+      <c r="AV142">
+        <v>13</v>
+      </c>
+      <c r="AW142">
+        <v>13</v>
+      </c>
+      <c r="AX142">
+        <v>13</v>
+      </c>
+      <c r="AY142">
+        <v>13</v>
+      </c>
+      <c r="AZ142">
+        <v>13</v>
+      </c>
+      <c r="BA142">
+        <v>13</v>
+      </c>
+      <c r="BB142">
+        <v>13</v>
+      </c>
+      <c r="BC142">
+        <v>13</v>
+      </c>
+      <c r="BD142">
+        <v>13</v>
+      </c>
+      <c r="BE142">
+        <v>13</v>
+      </c>
+      <c r="BF142">
+        <v>13</v>
+      </c>
+      <c r="BG142">
+        <v>13</v>
+      </c>
+      <c r="BH142">
+        <v>13</v>
+      </c>
+      <c r="BI142">
+        <v>13</v>
+      </c>
+      <c r="BJ142">
+        <v>13</v>
       </c>
       <c r="BK142">
         <v>13</v>

--- a/media/Levels/Level_8.xlsx
+++ b/media/Levels/Level_8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34D34B72-7BF8-4F82-A441-D0B8328CA234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D27503-1369-4EA7-BC83-462530B86B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="BW1" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX1" s="1">
         <v>0</v>
       </c>
       <c r="BY1" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BZ1" s="1">
         <v>0</v>
@@ -68625,13 +68625,13 @@
         <v>0</v>
       </c>
       <c r="BW150" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BX150" s="1">
         <v>0</v>
       </c>
       <c r="BY150" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BZ150" s="1">
         <v>0</v>

--- a/media/Levels/Level_8.xlsx
+++ b/media/Levels/Level_8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D27503-1369-4EA7-BC83-462530B86B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D0E83A-0E55-4BCF-AFBC-3334EB1C02C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
@@ -33599,7 +33599,7 @@
     </row>
     <row r="73" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B73">
         <v>13</v>
@@ -34046,12 +34046,12 @@
         <v>13</v>
       </c>
       <c r="ET73" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:150" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B74" s="1">
         <v>0</v>
@@ -34498,7 +34498,7 @@
         <v>0</v>
       </c>
       <c r="ET74" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:150" x14ac:dyDescent="0.45">

--- a/media/Levels/Level_8.xlsx
+++ b/media/Levels/Level_8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D27503-1369-4EA7-BC83-462530B86B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C03BED-0D8E-4573-B3E2-75E78B54629D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
+    <workbookView minimized="1" xWindow="816" yWindow="972" windowWidth="17280" windowHeight="8880" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Level_8" sheetId="1" r:id="rId1"/>
